--- a/news_daily/2026-09-29.xlsx
+++ b/news_daily/2026-09-29.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,10 +92,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1161,6 +1189,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1323,6 +1355,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1358,28 +1394,32 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1419,7 +1459,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1428,7 +1468,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>59fdd64881ab4c5286817979ab4920cb</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>aedc89f15619faa7115528b6</t>
@@ -1449,7 +1493,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1493,346 +1541,370 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>FICO</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Fair Isaac Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Fair Isaac Shares Fall After FHFA Chief Says VantageScore Moving to FICO Classic Pricing Grid</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>'-0.902</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbDgxOGRiYnI0WVBEcGhCNFI4eG14cU9vM3F5UmNkbW5CLTY3SG91dnp1bjdQeWFJNEdKRXozYng4QlByS25LZngzTk16eWlsdkF4RXRKX2NNbWVFbEtmdEJjTEJOWEZZaVBjRkpPaS1UNUJ1TzFmYll6cFlWOUl3UkZ0TmNodTdVM2xRZEJsa0phNHRQY1cw?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>24286e1d4e4a2ee0a50595d9</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>12a5ab7e7760c0a17a8ab70f</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>FICO</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Netflix upgraded, PepsiCo downgraded: Wall Street's top analyst calls</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>'-0.137</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQOEhnMVhmd0JvVDYzZWdJNU5IbDNRYUtXVkpZT180MmtfWmdzUXdHNGRMME50bWNUdFFZRjRNSFVHZWlzN2NaUFR3RXprN2ZzZzZrNGdKYjFmNFN2M3BuajZhOUl5QS1NWWVtZGJEcXowOGh4NHE2N1Vwcmt1WU5sTERrdFVVa2lhYTlqWHRUdC1CTXBxQmtBNWpqUk16WGZKaE9odVVwZU0?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>7a41afc19b93779f3de2dd4c</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>167ccb5030b41f622ad5d634</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1868,28 +1940,32 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1929,7 +2005,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1938,7 +2014,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>140f9fcf114241ec9d2dc14f8470bd5f</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>6836a87b0fc07586b95c8eaa</t>
@@ -1959,7 +2039,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2003,346 +2087,370 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>PepsiCo, Inc.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Why PepsiCo just got hit with a downgrade despite the stock trading at a 52-week low</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>'-0.587</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNSnVfaWMyQ2dqdnBmTEhYemdKQXBLSzNWaF9MaHFSSWJsbEk3US1LV256Zm1walNhTWhSRVpFZ2g0T1lUTEoyR1drY2xPNVR1alVzU1d6T1ZQdGpDZndfWUdsLTRleU9HWDFoZ182a29XZUotRXZ6bFB4eUVVQXg5dkZ0RTJoenBGbHY4M3JrY0hoekdDMjNBRENBeW1HSDhtYzBmY3d0Z3BTN08xUzQ0WC16NUV6Z3hQeGtLNVNBQ0VZZlYyT3hVWXFHVVF5bzJuWlFQdXBQMlNKaHlBX3dxV29R?oc=5</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>aa0336c84343a08781dd326b</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AD9" s="3" t="inlineStr">
         <is>
           <t>05ed3aff967531cb612168d3</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="BC9" s="4" t="inlineStr">
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="4" t="inlineStr">
+      <c r="BF9" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="4" t="inlineStr">
+      <c r="BG9" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>VRTX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Vertex Pharmaceuticals- Still Too Much Emphasis On CF Supremacy - I Foresee A Downgrade</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>'-0.665</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPUFROWEpaeUhIV25tOExxMTMwREtJSENldXkydmNFLVdZRlhKbjFLZTY2dkhDTm1oM1dMVDBmalVxcmZEbjVzNTVSVUR3ZUl3MmFJYVE3bTRqNHJuTWxMQ1dZZTNXb0xxcTdWSUFPd2lvVTlyMG05eVVmajdKSkRFVWI3cFBUUmlkemdkWW1OTFY5Z3hNMHhnN1FtclVDbHkzcks0YlVyVDBkbW1XOWozOXFoazE1TW5Iam85SQ?oc=5</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>0f601f70e36177b987236d96</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AD10" s="3" t="inlineStr">
         <is>
           <t>60e3da6fc283fb660833d495</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
         <is>
           <t>VRTX</t>
         </is>
       </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2378,28 +2486,32 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2439,7 +2551,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2448,7 +2560,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>14dbaec746064027834b65927dd85eb3</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>e708b7ec3a31b4c79dbc8814</t>
@@ -2469,7 +2585,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2513,176 +2633,216 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>7ecc223a3a60484895aabdb0d59636c3</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>d03cf40dbaece8e0a66e1a06</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>9f43694b4dd2bd44dcd6790d</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>The Des Moines Register</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>d03cf40dbaece8e0a66e1a06</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>9f43694b4dd2bd44dcd6790d</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2718,28 +2878,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>內線交易</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2779,7 +2943,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>INSIDER_TRADING</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2788,7 +2952,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>2c475b11ba9442d6bcf3f199d5c6cf2f</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>bb09c8f822554dd359c34f44</t>
@@ -2809,7 +2977,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2853,9 +3025,25 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2866,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2929,6 +3117,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3230,6 +3422,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3402,6 +3614,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3564,6 +3780,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3726,859 +3946,207 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>US judge rejects class action over Energizer, Walmart battery prices</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>7ecc223a3a60484895aabdb0d59636c3</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>d03cf40dbaece8e0a66e1a06</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>9f43694b4dd2bd44dcd6790d</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.814</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQd3k2dURMNzRXNkgzS25PUy0tRkJ6UWlYUVdSNDhhcHdkbGJuVENCTmtsVURPX0ZnVlpQZ2l2MzhiT3Zrdmg2bjBQcm5LRFhmbGlpUHRVM1BfNFliR2pzTlQtaXh0WnQ0LTRwTnZBY05fQXUtejB3ZVpqb3NoTXpDZllJbEIzWUlxVG5kb1YwNEd3ZGpKMjJjWHlhN1YxX0gyT3k0VmdDM2JCZXAtaTd3YUw1ODlobTJvUGRrZQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>aedc89f15619faa7115528b6</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>7f3ec1945fddddab2bfb50ac</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CVS Settlement: How to File a Claim and Get $10</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.018</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVzVwdzliSHlYSERWMU9XN2Vrc1l5dXAyUlV5c3Yyb1dxckNYdWVqZUZGTzZ4ODJUbW5HRjNyaC12dWNhZ3RBV0hPRXlHX2pVbjBrRXhZZE9pazd3cjZDdWVzZHM0bnRPOVJXQkl4dW1TMkpVRkMxVXNsNF9WUG52d3U5cUlydw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>AARP</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>6836a87b0fc07586b95c8eaa</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>cd725062972ae3070819698b</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Here's how to file a claim for the $100 million Equifax credit reporting error class action settlement!</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQSjZUYzJMQ0kxYjlhXzZpX2ZseVJqejdGN055ci1qMzIySTVIczM2dUp6TkxnVUU3bnEtajZYMXRlQnlJbnEtRGNrUDUwa3QxSkR2RGgwU3dFZUtMbzJHd1JSd2Y1VVN2TlBWaFFlSFNzdkswMXhDd01DMHlYanVkRlJUTkZGQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>e708b7ec3a31b4c79dbc8814</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>9d5cde790d8c8317ea215eac</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>The Des Moines Register</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>d03cf40dbaece8e0a66e1a06</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>9f43694b4dd2bd44dcd6790d</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Jabil Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29T05:05:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>JABIL Q4 2026 Earnings Preview: Recent $JBL Insider Trading, Hedge Fund Activity, and More</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>內線交易</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.053</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQSDM4Y3Y5X0tGc2tSUmlsMTRkZTdQSE5oaGo4dXhsTDIwS0UyQVhxdHoxM1pJNWxvalVXVFRmTUNlSjBVWm84a1N5OXJpT2FOVENXSnQydUh1S1dJMG94andKT2FvZmJLLTBOOGpwaHhvSk9RVVBobTlNYzhsTDVteFQ2Nmw4bWdQSmtkNnp0V3FJZXJiU1pHaWxxMUthOXZWbTcwQ04wVkRGcG9Wc1RLX281TWxyd0lyVnVOWUdoSk0?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>INSIDER_TRADING</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>insider trading</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>bb09c8f822554dd359c34f44</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>4c91944f8ddb95b7bb45576e</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH9"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4589,7 +4157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4652,6 +4220,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4955,9 +4527,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4968,7 +4560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5031,6 +4623,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5334,9 +4930,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5347,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5397,477 +5013,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-29.xlsx
+++ b/news_daily/2026-09-29.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,18 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -888,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +954,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>13c12adce01e415dbac08c7d7bc28eae</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>c05de3b1b0b236ac97396804</t>
@@ -979,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1023,10 +1027,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1062,28 +1078,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1123,7 +1143,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>EXPORT_RESTRICTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1132,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>3cca8b9418a24a258250e4c429790df9</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>197eed93c7b518277979fe7b</t>
@@ -1153,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1189,10 +1217,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1228,28 +1268,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1289,7 +1333,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1298,7 +1342,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>044adba1e9bd4d0f95046f7357e3d659</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>488b4639b6b647bc1a908400</t>
@@ -1319,7 +1367,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1355,1688 +1407,1700 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Walmart Inc.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>US judge rejects class action over Energizer, Walmart battery prices</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.814</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQd3k2dURMNzRXNkgzS25PUy0tRkJ6UWlYUVdSNDhhcHdkbGJuVENCTmtsVURPX0ZnVlpQZ2l2MzhiT3Zrdmg2bjBQcm5LRFhmbGlpUHRVM1BfNFliR2pzTlQtaXh0WnQ0LTRwTnZBY05fQXUtejB3ZVpqb3NoTXpDZllJbEIzWUlxVG5kb1YwNEd3ZGpKMjJjWHlhN1YxX0gyT3k0VmdDM2JCZXAtaTd3YUw1ODlobTJvUGRrZQ?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>class action</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>59fdd64881ab4c5286817979ab4920cb</t>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>aedc89f15619faa7115528b6</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>7f3ec1945fddddab2bfb50ac</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr">
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr">
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL5" s="3" t="inlineStr">
+      <c r="BL5" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>FICO</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fair Isaac Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Fair Isaac Shares Fall After FHFA Chief Says VantageScore Moving to FICO Classic Pricing Grid</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>'-0.902</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbDgxOGRiYnI0WVBEcGhCNFI4eG14cU9vM3F5UmNkbW5CLTY3SG91dnp1bjdQeWFJNEdKRXozYng4QlByS25LZngzTk16eWlsdkF4RXRKX2NNbWVFbEtmdEJjTEJOWEZZaVBjRkpPaS1UNUJ1TzFmYll6cFlWOUl3UkZ0TmNodTdVM2xRZEJsa0phNHRQY1cw?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>24286e1d4e4a2ee0a50595d9</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>12a5ab7e7760c0a17a8ab70f</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>FICO</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Netflix upgraded, PepsiCo downgraded: Wall Street's top analyst calls</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>'-0.137</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQOEhnMVhmd0JvVDYzZWdJNU5IbDNRYUtXVkpZT180MmtfWmdzUXdHNGRMME50bWNUdFFZRjRNSFVHZWlzN2NaUFR3RXprN2ZzZzZrNGdKYjFmNFN2M3BuajZhOUl5QS1NWWVtZGJEcXowOGh4NHE2N1Vwcmt1WU5sTERrdFVVa2lhYTlqWHRUdC1CTXBxQmtBNWpqUk16WGZKaE9odVVwZU0?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>7a41afc19b93779f3de2dd4c</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>167ccb5030b41f622ad5d634</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>CVS Settlement: How to File a Claim and Get $10</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0.018</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVzVwdzliSHlYSERWMU9XN2Vrc1l5dXAyUlV5c3Yyb1dxckNYdWVqZUZGTzZ4ODJUbW5HRjNyaC12dWNhZ3RBV0hPRXlHX2pVbjBrRXhZZE9pazd3cjZDdWVzZHM0bnRPOVJXQkl4dW1TMkpVRkMxVXNsNF9WUG52d3U5cUlydw?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>AARP</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>140f9fcf114241ec9d2dc14f8470bd5f</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>6836a87b0fc07586b95c8eaa</t>
         </is>
       </c>
-      <c r="AD8" s="3" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>cd725062972ae3070819698b</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr">
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr">
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL8" s="3" t="inlineStr">
+      <c r="BL8" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>PepsiCo, Inc.</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Why PepsiCo just got hit with a downgrade despite the stock trading at a 52-week low</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>'-0.587</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNSnVfaWMyQ2dqdnBmTEhYemdKQXBLSzNWaF9MaHFSSWJsbEk3US1LV256Zm1walNhTWhSRVpFZ2g0T1lUTEoyR1drY2xPNVR1alVzU1d6T1ZQdGpDZndfWUdsLTRleU9HWDFoZ182a29XZUotRXZ6bFB4eUVVQXg5dkZ0RTJoenBGbHY4M3JrY0hoekdDMjNBRENBeW1HSDhtYzBmY3d0Z3BTN08xUzQ0WC16NUV6Z3hQeGtLNVNBQ0VZZlYyT3hVWXFHVVF5bzJuWlFQdXBQMlNKaHlBX3dxV29R?oc=5</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>aa0336c84343a08781dd326b</t>
         </is>
       </c>
-      <c r="AD9" s="3" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>05ed3aff967531cb612168d3</t>
         </is>
       </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>VRTX</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Vertex Pharmaceuticals- Still Too Much Emphasis On CF Supremacy - I Foresee A Downgrade</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>'-0.665</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPUFROWEpaeUhIV25tOExxMTMwREtJSENldXkydmNFLVdZRlhKbjFLZTY2dkhDTm1oM1dMVDBmalVxcmZEbjVzNTVSVUR3ZUl3MmFJYVE3bTRqNHJuTWxMQ1dZZTNXb0xxcTdWSUFPd2lvVTlyMG05eVVmajdKSkRFVWI3cFBUUmlkemdkWW1OTFY5Z3hNMHhnN1FtclVDbHkzcks0YlVyVDBkbW1XOWozOXFoazE1TW5Iam85SQ?oc=5</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>0f601f70e36177b987236d96</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>60e3da6fc283fb660833d495</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>VRTX</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Here's how to file a claim for the $100 million Equifax credit reporting error class action settlement!</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQSjZUYzJMQ0kxYjlhXzZpX2ZseVJqejdGN055ci1qMzIySTVIczM2dUp6TkxnVUU3bnEtajZYMXRlQnlJbnEtRGNrUDUwa3QxSkR2RGgwU3dFZUtMbzJHd1JSd2Y1VVN2TlBWaFFlSFNzdkswMXhDd01DMHlYanVkRlJUTkZGQQ?oc=5</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Claim Depot</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>14dbaec746064027834b65927dd85eb3</t>
         </is>
       </c>
-      <c r="AC11" s="3" t="inlineStr">
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>e708b7ec3a31b4c79dbc8814</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="inlineStr">
+      <c r="AD11" s="2" t="inlineStr">
         <is>
           <t>9d5cde790d8c8317ea215eac</t>
         </is>
       </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr">
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL11" s="3" t="inlineStr">
+      <c r="BL11" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>0.215</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t>The Des Moines Register</t>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>REGULATORY_PENALTY</t>
         </is>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>7ecc223a3a60484895aabdb0d59636c3</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>d03cf40dbaece8e0a66e1a06</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AD12" s="3" t="inlineStr">
         <is>
           <t>9f43694b4dd2bd44dcd6790d</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BG12" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr">
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="4" t="inlineStr">
+      <c r="BL12" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Jabil Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-09-29T05:05:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>JABIL Q4 2026 Earnings Preview: Recent $JBL Insider Trading, Hedge Fund Activity, and More</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>'-0.053</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQSDM4Y3Y5X0tGc2tSUmlsMTRkZTdQSE5oaGo4dXhsTDIwS0UyQVhxdHoxM1pJNWxvalVXVFRmTUNlSjBVWm84a1N5OXJpT2FOVENXSnQydUh1S1dJMG94andKT2FvZmJLLTBOOGpwaHhvSk9RVVBobTlNYzhsTDVteFQ2Nmw4bWdQSmtkNnp0V3FJZXJiU1pHaWxxMUthOXZWbTcwQ04wVkRGcG9Wc1RLX281TWxyd0lyVnVOWUdoSk0?oc=5</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Quiver Quantitative</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>GOVERNANCE</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>insider trading</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>2c475b11ba9442d6bcf3f199d5c6cf2f</t>
         </is>
       </c>
-      <c r="AC13" s="3" t="inlineStr">
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>bb09c8f822554dd359c34f44</t>
         </is>
       </c>
-      <c r="AD13" s="3" t="inlineStr">
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>4c91944f8ddb95b7bb45576e</t>
         </is>
       </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
       </c>
-      <c r="BC13" s="3" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF13" s="3" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG13" s="3" t="inlineStr">
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr">
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr">
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL13" s="3" t="inlineStr">
+      <c r="BL13" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -3054,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3446,707 +3510,201 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Ball Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-29T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Ball State’s Logistics and Supply Chain Management Program Earns STEM Designation</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>7ecc223a3a60484895aabdb0d59636c3</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>d03cf40dbaece8e0a66e1a06</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>9f43694b4dd2bd44dcd6790d</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPSy03OHpHNE1WV0pXbk5KczdkUU9MRmZMZHZ0S3otSnd1OGoyTVUwLVYxMHZzUS10cGNxLWtzalM0UlF4OGhxX1FXb2s2R3VfcUxuMDNFbUh1SUNWRjdTQmMzODdDdnBNV01ZMGlscTJ5T3IxZlZZWFdRNEhqWE9qSnFNTGhWZzRqTW80M2hSSUYzQmlmZXlvTlVNM3FZZjgySk5EYk1nVWxqWkp2S0VfWG5nV0VFMF9pS3VhWUhVTXBOckc4YzYtQU9VWFlFMTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Ball State University</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>c05de3b1b0b236ac97396804</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>d1132d531836887b9dc86f6c</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>BALL</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr">
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>ExxonMobil Got a $180 Target as Trump Weighed a Diesel Export Ban. Here’s What It Means for the Stock</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>出口管制</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.053</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZ0xqbTktTTFqSllfRWNCN0FCWmdfakZFLXlaMEU0aG5zT0pOQ3BtZG1PWTlOOVJmZ2xIRkNiN2F3UUQ4dllQOV9Vd3NwNlhOdDFGMm16YXluUnMyOUVtbkNYMG1KRmxSakticFhGT18xNlkwbmdZM05kNDZ2eWRWLWFjZ29zYi1fVGI3ZzNnYWNJQTJ6emZmVFJTT1NXYlU5S3hpdzhhQjVSYjNYYjZ1ajV0czVhalVtd1d5SWtuSjhEQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>TIKR.com</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>197eed93c7b518277979fe7b</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>7c39112bfd50c2aee6447560</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Cisco president Jeetu Patel says AI will create more jobs than it eliminates despite tech layoffs -- EXCLUSIVE</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.231</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxONjU4aFh0SHR1ZE9IeWFTdDZNTi16b01mZDh3ZHNEZG9iNV9OeVBiY2pLblY2N21ocjNya1lIci1UWk5fcFJmNDFpVVRwRnVPSzZpY19YeUR5dkY3X2RfeGo4dFlDTTVJUlgwTTU5N3RQT1lJZmw5eDNNV1RndjZ1TFZQdnZuWnZWSmJhSFlTX1lTSDRrbzNQTGRrVjlkU2ZZa1IycFBleWcyTzVVcl9lejlROS1rQjVvWmJJUzNLNjNZM0ZlNTg4a0lqd2VidlZB0gHWAUFVX3lxTE9UalM0aV9IZVJoZEJVT2Zyc3JKMElxRFExa1pKeE9VcWpyT0ViYkp4TFJDNWJaMWQ1WFdLbWhDT0JCT0xnYUxPXzltZTJITzBpRTVJV2Q4Nlh6b3c2dGhQWFRSLTc1WmhWTFo4LW44d2RQVlNlc3NKaC1hcVNZaUpGZUVCTllGRWVPV1E3QjEyOVJ6dWJxY1RTZXpZbWRfZDZabTNjLWZ5RWdlRzVKTVRTNjhRdE5ZTmxTWjJmRmd1VnhxVDBkWFdGSGRxWFNGN1IzS05TWWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>ABC7 Bay Area</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>488b4639b6b647bc1a908400</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>4f29695288f851e4f759c483</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr"/>
-      <c r="BG4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Iowa, other attorneys general, FTC, reach settlement with Corteva</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPOVZyWV9Ka1RuS2VlRVlrWTZqLTRSbk9ybzBoYUtaSWNTNEoyeEZBSWM3bUluNnlrN0xpXzRublBxZ2JNVWhZN0xXSE9Ia3oyaEdZNWVXZnpMaVpBdm5ZSFJscHZDZHg5SnN6aHdiNHVyUERjS214aXdONGZGWWhGRHdkbzEtTG85d2p0dFhoYWY4dXJteEIyMlotd0RxdlRGdGdlUGdyc1BxLTZhYlRkX1AtSmw0bHlkMHRTM0xpTkI0LWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>The Des Moines Register</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>7ecc223a3a60484895aabdb0d59636c3</t>
-        </is>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>d03cf40dbaece8e0a66e1a06</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>9f43694b4dd2bd44dcd6790d</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr">
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL5" s="4" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL5"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5133,645 +4691,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="3" t="b">
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="3" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="2" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="3" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="2" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="2" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="2" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="n">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="b">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="3" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="3" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>

--- a/news_daily/2026-09-29.xlsx
+++ b/news_daily/2026-09-29.xlsx
@@ -1671,13 +1671,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1726,7 +1730,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>4505c6df92a0460db2c80b1e524cc7bb</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>24286e1d4e4a2ee0a50595d9</t>
@@ -1747,7 +1755,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1793,8 +1805,16 @@
       <c r="BH6" s="2" t="inlineStr"/>
       <c r="BI6" s="2" t="inlineStr"/>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1830,28 +1850,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1891,7 +1915,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1900,7 +1924,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>733510709a314c928aa443519adfeff8</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>7a41afc19b93779f3de2dd4c</t>
@@ -1921,7 +1949,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1965,10 +1997,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2217,13 +2261,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2272,7 +2320,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>3367b8e3a71243b0a2832c7155846c93</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>aa0336c84343a08781dd326b</t>
@@ -2293,7 +2345,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2339,8 +2395,16 @@
       <c r="BH9" s="2" t="inlineStr"/>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2376,28 +2440,32 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2437,7 +2505,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2446,7 +2514,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>c6f807871e004d0fb1ba42d469f1f3af</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>0f601f70e36177b987236d96</t>
@@ -2467,7 +2539,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2511,10 +2587,22 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
